--- a/artfynd/A 15285-2026 artfynd.xlsx
+++ b/artfynd/A 15285-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>55519386</v>
       </c>
       <c r="B2" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624370.5726846659</v>
+        <v>624371</v>
       </c>
       <c r="R2" t="n">
-        <v>6352898.318779265</v>
+        <v>6352898</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -791,49 +786,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Per Backman, Naja Magnusson </t>
+          <t>Per Backman, Naja Sköldén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55519412</v>
+        <v>55519404</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -849,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624370.5726846659</v>
+        <v>624371</v>
       </c>
       <c r="R3" t="n">
-        <v>6352898.318779265</v>
+        <v>6352898</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -914,10 +904,128 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Per Backman, Naja Magnusson </t>
+          <t>Per Backman, Naja Sköldén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>55519412</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Getterum, kärr 1400 SSO, Öl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>624371</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6352898</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-10-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-10-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Backman, Naja Sköldén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15285-2026 artfynd.xlsx
+++ b/artfynd/A 15285-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55519386</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55519404</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,8 +1041,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55519412</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>